--- a/dev_docs/马娘技能表.xlsx
+++ b/dev_docs/马娘技能表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\AppData\Roaming\PrismLauncher\instances\SenDimsBanForges\minecraft\dev_docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\Documents\EX\HMCL\.minecraft\versions\SDBF\dev_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{090E3C04-73AA-4FE6-8EC5-5D95A72F866C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16E88EAB-9E85-4F0B-B1FF-E306F7DD85FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30612" yWindow="-6720" windowWidth="30936" windowHeight="18816" xr2:uid="{2DF2D3CD-81A7-44E3-987F-5ED6090C2776}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="114">
   <si>
     <t>技能名称 (ID)</t>
   </si>
@@ -2455,10 +2455,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>古代知识I+生命恢复I+伤害吸收I，持续时间200；干劲+1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>速度III，100</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -2584,6 +2580,10 @@
   </si>
   <si>
     <t>给予附近敌人重伤II-IIII，持续时间300-400，移除焦躁，干劲+1，低血量时干劲额外+1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>古代知识I+生命恢复I+伤害吸收II，持续时间200；干劲+1</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2988,7 +2988,7 @@
   <sheetData>
     <row r="3" spans="2:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>0</v>
@@ -3009,10 +3009,10 @@
         <v>18</v>
       </c>
       <c r="J3" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="4" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3033,13 +3033,13 @@
         <v>14</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="2:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3062,13 +3062,13 @@
         <v>19</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J5" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="6" spans="2:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3089,13 +3089,13 @@
         <v>20</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J6" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="K6" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="7" spans="2:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3118,7 +3118,7 @@
         <v>21</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="2:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3139,7 +3139,7 @@
         <v>22</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="2:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3162,7 +3162,7 @@
         <v>23</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="2:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3183,7 +3183,7 @@
         <v>24</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="2:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3204,7 +3204,7 @@
         <v>15</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="2:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3227,7 +3227,7 @@
         <v>25</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="2:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3248,22 +3248,22 @@
         <v>26</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J13" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K13" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="K13" s="3" t="s">
+      <c r="L13" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="L13" s="3" t="s">
+      <c r="M13" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="M13" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="N13" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="2:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3284,7 +3284,7 @@
         <v>27</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="2:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3305,7 +3305,7 @@
         <v>28</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="2:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3328,7 +3328,7 @@
         <v>29</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3349,10 +3349,13 @@
         <v>30</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" spans="2:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="3">
+        <v>1</v>
+      </c>
       <c r="C18" s="1" t="s">
         <v>5</v>
       </c>
@@ -3371,6 +3374,9 @@
       </c>
     </row>
     <row r="19" spans="2:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="3">
+        <v>1</v>
+      </c>
       <c r="C19" s="1" t="s">
         <v>6</v>
       </c>
@@ -3385,10 +3391,13 @@
         <v>17</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="2:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="3">
+        <v>0</v>
+      </c>
       <c r="C20" s="1" t="s">
         <v>57</v>
       </c>
@@ -3405,10 +3414,13 @@
         <v>31</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="3">
+        <v>0</v>
+      </c>
       <c r="C21" s="1" t="s">
         <v>59</v>
       </c>
@@ -3423,7 +3435,7 @@
         <v>33</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="2:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3441,7 +3453,7 @@
         <v>34</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="2:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3457,7 +3469,7 @@
         <v>35</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" spans="2:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3473,7 +3485,7 @@
         <v>36</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3489,7 +3501,7 @@
         <v>37</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="2:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3505,7 +3517,7 @@
         <v>38</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3521,12 +3533,12 @@
         <v>39</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="2:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D28" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>8</v>
@@ -3534,7 +3546,7 @@
     </row>
     <row r="29" spans="2:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D29" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>8</v>

--- a/dev_docs/马娘技能表.xlsx
+++ b/dev_docs/马娘技能表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\Documents\EX\HMCL\.minecraft\versions\SDBF\dev_docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\AppData\Roaming\PrismLauncher\instances\SenDimsBanForges\minecraft\dev_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16E88EAB-9E85-4F0B-B1FF-E306F7DD85FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C35ED542-395D-4D72-9A76-1DF21F73DDEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30612" yWindow="-6720" windowWidth="30936" windowHeight="18816" xr2:uid="{2DF2D3CD-81A7-44E3-987F-5ED6090C2776}"/>
   </bookViews>
@@ -2507,14 +2507,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>范围减速I+虚弱I，200</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>范围减速I，200</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>完成</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -2584,6 +2576,14 @@
   </si>
   <si>
     <t>古代知识I+生命恢复I+伤害吸收II，持续时间200；干劲+1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>范围减速IV，200</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>范围减速IV+虚弱I，200</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2988,7 +2988,7 @@
   <sheetData>
     <row r="3" spans="2:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>0</v>
@@ -3009,10 +3009,10 @@
         <v>18</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3036,10 +3036,10 @@
         <v>88</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="2:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3065,10 +3065,10 @@
         <v>81</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="2:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3089,13 +3089,13 @@
         <v>20</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="2:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3118,7 +3118,7 @@
         <v>21</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="2:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3139,7 +3139,7 @@
         <v>22</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="2:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3263,7 +3263,7 @@
         <v>87</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="2:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3284,7 +3284,7 @@
         <v>27</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="2:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3305,7 +3305,7 @@
         <v>28</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="2:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3328,7 +3328,7 @@
         <v>29</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3349,7 +3349,7 @@
         <v>30</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" spans="2:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3391,12 +3391,12 @@
         <v>17</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="2:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>57</v>
@@ -3414,12 +3414,12 @@
         <v>31</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>59</v>
@@ -3435,7 +3435,7 @@
         <v>33</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" spans="2:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">

--- a/dev_docs/马娘技能表.xlsx
+++ b/dev_docs/马娘技能表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\AppData\Roaming\PrismLauncher\instances\SenDimsBanForges\minecraft\dev_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C35ED542-395D-4D72-9A76-1DF21F73DDEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4568A7FB-54E2-4A03-B90B-819E8B6918B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-6720" windowWidth="30936" windowHeight="18816" xr2:uid="{2DF2D3CD-81A7-44E3-987F-5ED6090C2776}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{2DF2D3CD-81A7-44E3-987F-5ED6090C2776}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2495,26 +2495,14 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>速度III+力量II,160</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>速度II+力量I,100</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>速度II，100；干劲+1；治疗5%最大生命值，最低4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>完成</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>速度III-IV，160；给予附近敌人破甲I，20-80</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>&gt;25000,VI</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -2575,15 +2563,27 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>古代知识I+生命恢复I+伤害吸收II，持续时间200；干劲+1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>范围减速IV，200</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>范围减速IV+虚弱I，200</t>
+    <t>速度III-IV，160；给予附近敌人破甲I，100-200</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>速度III+力量II,200</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>速度II，100；干劲+1；治疗15%最大生命值，最低4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>古代知识I+生命恢复II+伤害吸收II，持续时间400；干劲+1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>范围减速IV+虚弱II，300</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>范围减速IV+虚弱IV，300</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2988,7 +2988,7 @@
   <sheetData>
     <row r="3" spans="2:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>0</v>
@@ -3009,10 +3009,10 @@
         <v>18</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="2:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3036,10 +3036,10 @@
         <v>88</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="2:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3065,10 +3065,10 @@
         <v>81</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="2:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3089,13 +3089,13 @@
         <v>20</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="2:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3118,7 +3118,7 @@
         <v>21</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="2:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3139,7 +3139,7 @@
         <v>22</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="2:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3162,7 +3162,7 @@
         <v>23</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="2:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3183,7 +3183,7 @@
         <v>24</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="2:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3204,7 +3204,7 @@
         <v>15</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="2:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3263,7 +3263,7 @@
         <v>87</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="2:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3284,7 +3284,7 @@
         <v>27</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="2:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3305,7 +3305,7 @@
         <v>28</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" spans="2:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3328,7 +3328,7 @@
         <v>29</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -3349,7 +3349,7 @@
         <v>30</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" spans="2:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
